--- a/Config/Excel/Tables/Unit表.xlsx
+++ b/Config/Excel/Tables/Unit表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -35,82 +35,37 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Desc</t>
+    <t>UnitType</t>
   </si>
   <si>
     <t>Position</t>
   </si>
   <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
+    <t>Unit类型</t>
+  </si>
+  <si>
     <t>测试说明</t>
   </si>
   <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
     <t>位置</t>
   </si>
   <si>
-    <t>身高</t>
-  </si>
-  <si>
-    <t>体重</t>
-  </si>
-  <si>
-    <t>米克尔</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能</t>
-  </si>
-  <si>
-    <t>测试说明2</t>
-  </si>
-  <si>
-    <t>米克尔2</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能2</t>
-  </si>
-  <si>
-    <t>米克尔3</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能3</t>
-  </si>
-  <si>
-    <t>米克尔4</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能4</t>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>怪物</t>
+  </si>
+  <si>
+    <t>NPC</t>
   </si>
 </sst>
 </file>
@@ -750,7 +705,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -760,9 +715,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1111,22 +1063,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.1203703703704" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.1166666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.6296296296296" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.1203703703704" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.62962962962963" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.87962962962963" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="12.6333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.875" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" spans="1:9">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1140,79 +1088,40 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="14.4" spans="1:10">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" ht="14.4" spans="1:9">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="4" ht="26.4" spans="1:9">
+    <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -1221,105 +1130,51 @@
         <v>5001</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="H4" s="1">
-        <v>178</v>
-      </c>
-      <c r="I4" s="1">
-        <v>68</v>
-      </c>
     </row>
-    <row r="5" ht="26.4" spans="1:9">
+    <row r="5" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
       <c r="C5" s="1">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="1">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1">
         <v>2</v>
       </c>
-      <c r="H5" s="1">
-        <v>278</v>
-      </c>
-      <c r="I5" s="1">
-        <v>78</v>
-      </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="26.4" spans="2:9">
+    <row r="6" s="1" customFormat="1" spans="1:6">
       <c r="B6" s="1">
         <v>1003</v>
       </c>
       <c r="C6" s="1">
-        <v>5001</v>
+        <v>5003</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="1">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1">
-        <v>178</v>
-      </c>
-      <c r="I6" s="1">
-        <v>68</v>
-      </c>
+      <c r="F6"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="26.4" spans="2:9">
-      <c r="B7" s="1">
-        <v>1004</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5001</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1">
-        <v>278</v>
-      </c>
-      <c r="I7" s="1">
-        <v>78</v>
-      </c>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="F7"/>
     </row>
-    <row r="8" s="1" customFormat="1"/>
-    <row r="9" s="1" customFormat="1"/>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="F8"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="F9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
